--- a/artfynd/A 3410-2022 artfynd.xlsx
+++ b/artfynd/A 3410-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3410-2022 artfynd.xlsx
+++ b/artfynd/A 3410-2022 artfynd.xlsx
@@ -14161,7 +14161,7 @@
         <v>120752070</v>
       </c>
       <c r="B122" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>

--- a/artfynd/A 3410-2022 artfynd.xlsx
+++ b/artfynd/A 3410-2022 artfynd.xlsx
@@ -14161,7 +14161,7 @@
         <v>120752070</v>
       </c>
       <c r="B122" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>

--- a/artfynd/A 3410-2022 artfynd.xlsx
+++ b/artfynd/A 3410-2022 artfynd.xlsx
@@ -14161,7 +14161,7 @@
         <v>120752070</v>
       </c>
       <c r="B122" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>

--- a/artfynd/A 3410-2022 artfynd.xlsx
+++ b/artfynd/A 3410-2022 artfynd.xlsx
@@ -14161,7 +14161,7 @@
         <v>120752070</v>
       </c>
       <c r="B122" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>

--- a/artfynd/A 3410-2022 artfynd.xlsx
+++ b/artfynd/A 3410-2022 artfynd.xlsx
@@ -1722,7 +1722,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
@@ -2253,7 +2253,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">

--- a/artfynd/A 3410-2022 artfynd.xlsx
+++ b/artfynd/A 3410-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY131"/>
+  <dimension ref="A1:AZ131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165650</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165644</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165239</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882207</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165284</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882206</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1419,6 +1454,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882238</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882289</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1631,6 +1676,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165248</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165257</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1853,6 +1908,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165261</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1964,6 +2024,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165294</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2075,6 +2140,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165313</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2186,6 +2256,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165324</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2297,6 +2372,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165253</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2408,6 +2488,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165283</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2519,6 +2604,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165322</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2630,6 +2720,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165570</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2741,6 +2836,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165328</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2852,6 +2952,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165640</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2962,6 +3067,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165300</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3073,6 +3183,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165323</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3180,6 +3295,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165245</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3287,6 +3407,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165320</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3394,6 +3519,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165648</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3501,6 +3631,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165654</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3613,6 +3748,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165666</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3724,6 +3864,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165266</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3835,6 +3980,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165288</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3946,6 +4096,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165645</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4047,6 +4202,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882210</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4158,6 +4318,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165247</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4269,6 +4434,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165282</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4380,6 +4550,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165286</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4491,6 +4666,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165652</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4592,6 +4772,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882228</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4703,6 +4888,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165236</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4814,6 +5004,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165254</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4925,6 +5120,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165314</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5026,6 +5226,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882209</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5137,6 +5342,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165285</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5248,6 +5458,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165289</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5359,6 +5574,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165318</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5470,6 +5690,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165638</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5581,6 +5806,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165287</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5692,6 +5922,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165312</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5793,6 +6028,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882220</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5894,6 +6134,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882283</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6005,6 +6250,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165268</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6116,6 +6366,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165279</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6227,6 +6482,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165301</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6338,6 +6598,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165302</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6449,6 +6714,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165308</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6560,6 +6830,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165315</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6671,6 +6946,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165340</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6782,6 +7062,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165653</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6893,6 +7178,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165675</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7004,6 +7294,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165305</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7105,6 +7400,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882253</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7216,6 +7516,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165238</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7327,6 +7632,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165242</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7438,6 +7748,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165319</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7549,6 +7864,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165639</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7660,6 +7980,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165662</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7761,6 +8086,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882202</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7862,6 +8192,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882217</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7963,6 +8298,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882224</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8064,6 +8404,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882237</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8165,6 +8510,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882239</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8266,6 +8616,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882290</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8377,6 +8732,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165250</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8488,6 +8848,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165256</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8599,6 +8964,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165262</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8710,6 +9080,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165273</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8821,6 +9196,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165280</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8932,6 +9312,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165295</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9043,6 +9428,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165309</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9154,6 +9544,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165325</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9265,6 +9660,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165333</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9376,6 +9776,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165656</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9487,6 +9892,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165660</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9598,6 +10008,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165663</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9709,6 +10124,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165676</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9820,6 +10240,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165292</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9921,6 +10346,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882219</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10022,6 +10452,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882225</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10123,6 +10558,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882215</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10224,6 +10664,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882270</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10325,6 +10770,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882275</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10426,6 +10876,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882221</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10527,6 +10982,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882204</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10628,6 +11088,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882223</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10729,6 +11194,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882231</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10830,6 +11300,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882232</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10931,6 +11406,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882276</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11032,6 +11512,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882281</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11133,6 +11618,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882235</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11234,6 +11724,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882241</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11335,6 +11830,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882247</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11436,6 +11936,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882245</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11537,6 +12042,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882211</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11638,6 +12148,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882218</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11739,6 +12254,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882236</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11840,6 +12360,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882286</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11947,6 +12472,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120752070</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12049,6 +12579,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298439</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12150,6 +12685,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882203</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12251,6 +12791,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882212</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12352,6 +12897,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882213</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12453,6 +13003,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882216</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12554,6 +13109,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882242</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12655,6 +13215,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882244</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12756,6 +13321,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882273</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12857,6 +13427,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882277</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12958,6 +13533,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882280</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13059,6 +13639,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882282</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13160,6 +13745,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882284</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13271,6 +13861,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165327</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13382,6 +13977,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165339</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13493,6 +14093,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165298</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13604,6 +14209,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165255</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13715,6 +14325,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165272</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13826,6 +14441,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165641</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13937,6 +14557,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165278</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14039,6 +14664,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882230</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14141,6 +14771,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882252</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14242,6 +14877,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882229</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14353,6 +14993,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165290</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14464,6 +15109,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165651</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14575,8 +15225,145 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165276</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>